--- a/astro-site/public/dl/hotel-checklist-templates/18-hotel-daily-opening-closing-rounds.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/18-hotel-daily-opening-closing-rounds.xlsx
@@ -809,7 +809,7 @@
     <row r="37" ht="48" customHeight="1">
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>▸ Order of use: shop → register. Each file covers one level: the shop file marks the MILESTONE (turn on, open, close) and the cash file carries the MONEY. If a task shows up in both, it's on purpose: one is the milestone and the other the detail.</t>
+          <t>▸ Order of use: rounds → cash drawer. Each file covers one level: the rounds file marks the MILESTONE (turn on, open, close) and the cash file carries the MONEY. If a task shows up in both, it's on purpose: one is the milestone and the other the detail.</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Opening Rounds — Full Hotel</t>
+          <t>Opening Rounds — F&amp;B Outlets &amp; Public Areas</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Front desk</t>
+          <t>Host stand</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Front desk</t>
+          <t>Host stand</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Closing Rounds — Full Hotel</t>
+          <t>Closing Rounds — F&amp;B Outlets &amp; Public Areas</t>
         </is>
       </c>
     </row>
